--- a/data/trans_bre/IQ2606_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IQ2606_R2-Estudios-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,64</t>
+          <t>-2,92</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>-3,67%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 21,64</t>
+          <t>-2,95; 22,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 20,5</t>
+          <t>-6,71; 21,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,45; 27,6</t>
+          <t>-36,21; 24,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 45,73</t>
+          <t>-5,36; 50,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 41,23</t>
+          <t>-10,74; 42,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,64; 42,76</t>
+          <t>-42,82; 36,18</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-1,77</t>
+          <t>-2,62</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-2,06%</t>
+          <t>-3,05%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 9,56</t>
+          <t>-1,66; 9,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 4,82</t>
+          <t>-4,95; 4,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 7,08</t>
+          <t>-11,72; 5,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 18,26</t>
+          <t>-2,7; 17,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 6,86</t>
+          <t>-6,73; 5,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 8,72</t>
+          <t>-13,24; 6,86</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,79</t>
+          <t>-4,1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,37%</t>
+          <t>-4,72%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 11,46</t>
+          <t>-5,18; 12,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 3,45</t>
+          <t>-11,13; 3,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 10,07</t>
+          <t>-17,14; 10,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 18,31</t>
+          <t>-7,31; 19,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 4,53</t>
+          <t>-13,03; 4,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 12,43</t>
+          <t>-18,47; 13,05</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-2,02</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-2,36%</t>
+          <t>-3,42%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 8,78</t>
+          <t>-0,27; 8,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 3,67</t>
+          <t>-3,85; 3,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 4,45</t>
+          <t>-9,98; 3,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 15,99</t>
+          <t>-0,48; 15,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 5,13</t>
+          <t>-5,16; 4,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 5,39</t>
+          <t>-11,35; 4,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2606_R2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IQ2606_R2-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -520,7 +529,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más, siempre o casi siempre</t>
+          <t>Menores que el verano pasado emplearon crema solar con factor de protección de 50 o más, siempre o casi siempre</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>9,92</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6,75</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,92</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18,68%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,64%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-3,67%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>9.916222986049284</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>6.748812552518113</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-2.918422819572408</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.1868085892139563</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1164105616484587</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.03674588666125002</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-2,95; 22,22</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,71; 21,8</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-36,21; 24,75</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-5,36; 50,38</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-10,74; 42,16</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-42,82; 36,18</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.950433259077186</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.705999008468795</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-36.21041312222867</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.0535639193715268</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1074095809432019</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.42819792259043</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>22.21994241078363</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>21.79999784469986</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>24.75215342300459</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.5037693795577282</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.4216116451343779</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.361795862796699</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,84</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,62</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-0,18%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-3,05%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,66; 9,29</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,95; 4,1</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-11,72; 5,53</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,7; 17,9</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-6,73; 5,83</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-13,24; 6,86</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>3.841142417367316</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.132091802444656</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.615480446638718</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.06960954661707368</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.001824215807680689</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.03046277858312934</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,41</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-3,71</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-4,1</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-4,53%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-4,72%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.655689644856492</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.9537626835567</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-11.72279977807679</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.02700740018107817</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.06730597561407275</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1324467240409902</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,18; 12,44</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-11,13; 3,61</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-17,14; 10,32</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-7,31; 19,93</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-13,03; 4,58</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-18,47; 13,05</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>9.293089469614815</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.100532817130611</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.526862770279284</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.1789610732160475</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.0583417366593238</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.06857125725799743</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +767,161 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4,59</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,93</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-0,46%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-3,42%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>3.405740173665572</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-3.707557660693539</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-4.098949863978651</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.05105447296521038</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.04533315149231424</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.04715073122840248</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,27; 8,49</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,85; 3,52</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-9,98; 3,72</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-0,48; 15,29</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-5,16; 4,93</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-11,35; 4,58</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.184419489203497</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-11.13493882131127</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-17.13975565441681</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.07306461724928186</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1302504481845479</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1847276187713009</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>12.43580733663681</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.607210299052849</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10.3160296787528</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.1993322736689072</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.04581290461677614</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1305246224397953</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>4.585368388393762</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.3351055993549013</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-2.929035505774136</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.07970041459553877</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.004566435591841512</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.03418950440371978</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.2711911645874739</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.854760058914387</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-9.980223839079811</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.004787540774170046</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.05163330710970351</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1135236177208179</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>8.494040127848878</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.520854276043286</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.723646708124626</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.1528652950195782</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.04932372641546322</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.0458041531729814</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -913,12 +930,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
